--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -690,99 +864,128 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>127961</v>
-      </c>
       <c r="N3" t="n">
-        <v>28894.41935483871</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>70</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9.05653082813039</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>cdc_weekly; nhc; pubmed</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>web; web; web</t>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-01-17</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1166,99 +1456,128 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>5</v>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
-        <v>0.004084042037828832</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>web</t>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1285,99 +1604,128 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1404,99 +1752,128 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>111021</v>
-      </c>
       <c r="N9" t="n">
-        <v>25069.25806451613</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>88</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7.857590274144966</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>cdc_weekly; nhc; pubmed</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>web; web; web</t>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1523,97 +1900,126 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1642,97 +2048,126 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1761,99 +2196,128 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>web</t>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1880,97 +2344,126 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1999,99 +2492,128 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2118,99 +2640,128 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>145066</v>
-      </c>
       <c r="N15" t="n">
-        <v>36266.5</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>136</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10.26714937452476</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>cdc_weekly; nhc; pubmed</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>web; web; web</t>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2237,97 +2788,126 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>0.004084042037828832</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2356,99 +2936,128 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>web</t>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2475,97 +3084,126 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>4</v>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="Q18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2594,97 +3232,126 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2713,99 +3380,128 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2832,99 +3528,128 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>135528</v>
-      </c>
       <c r="N21" t="n">
-        <v>30603.09677419355</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>173</v>
-      </c>
-      <c r="P21" t="n">
-        <v>9.592090637575945</v>
-      </c>
-      <c r="Q21" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>cdc_weekly; nhc; pubmed</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>web; web; web</t>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2951,99 +3676,128 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>web</t>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3070,97 +3824,126 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q23" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="AW23" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="BA23" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="BB23" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3189,97 +3972,126 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>2</v>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="Q24" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="AW24" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="BA24" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="BB24" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3308,97 +4120,126 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="P25" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="AW25" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="BB25" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3427,99 +4268,128 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3546,99 +4416,128 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>131378</v>
-      </c>
       <c r="N27" t="n">
-        <v>30654.86666666666</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>194</v>
-      </c>
-      <c r="P27" t="n">
-        <v>9.298371434562986</v>
-      </c>
-      <c r="Q27" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>cdc_weekly; nhc; pubmed</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>web; web; web</t>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3665,99 +4564,128 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="P28" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>web</t>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3784,97 +4712,126 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="Q29" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="AW29" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="BA29" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="BB29" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3903,97 +4860,126 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="AW30" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="BA30" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="BB30" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="BC30" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4022,97 +5008,126 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>3</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="Q31" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="AW31" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="BA31" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="BB31" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="BC31" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4141,97 +5156,126 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>3</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="Q32" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="AW32" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="BA32" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="BB32" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="BC32" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4260,46 +5304,48 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4307,50 +5353,77 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="AW33" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="BA33" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="BB33" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="BC33" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -4379,99 +5452,128 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>136295</v>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="N34" t="n">
-        <v>30776.29032258065</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>253</v>
-      </c>
-      <c r="P34" t="n">
-        <v>9.646375608349665</v>
-      </c>
-      <c r="Q34" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>cdc_weekly</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>cdc_weekly; nhc; pubmed</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>web; web; web</t>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4498,97 +5600,126 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>6</v>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="P35" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="AW35" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="BA35" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="BB35" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4617,97 +5748,126 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>6</v>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="Q36" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="AW36" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="BA36" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="BB36" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4736,97 +5896,126 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="Q37" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="AW37" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="BA37" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="BB37" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4855,97 +6044,126 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>7</v>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="Q38" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="AW38" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="BA38" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="BB38" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="BC38" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4974,46 +6192,48 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Viral Hepatitis</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>病毒性肝炎</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5021,764 +6241,77 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="AW39" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="AY39" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="BA39" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="BB39" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>viral-hepatitis</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>viral-hepatitis</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>viral-hepatitis</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.004084042037828832</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>viral-hepatitis</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>3</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>viral-hepatitis</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>viral-hepatitis</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>D006</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Viral Hepatitis</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
+      <c r="BC39" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -5896,62 +6429,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>787327</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -6317,6 +6317,154 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6350,7 +6498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -6443,7 +6591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -6495,7 +6643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -2985,9 +2985,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3722,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4613,9 +4607,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4752,6 @@
       <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.004900850445394598</v>
       </c>
@@ -4909,9 +4897,6 @@
       <c r="O30" t="n">
         <v>6</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.004900850445394598</v>
       </c>
@@ -5057,9 +5042,6 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -5205,9 +5187,6 @@
       <c r="O32" t="n">
         <v>7</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.005717658852960364</v>
       </c>
@@ -5353,9 +5332,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5477,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -5649,9 +5622,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -5797,9 +5767,6 @@
       <c r="O36" t="n">
         <v>5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -5945,9 +5912,6 @@
       <c r="O37" t="n">
         <v>3</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -6093,9 +6057,6 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -6241,9 +6202,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6388,9 +6346,6 @@
       </c>
       <c r="O40" t="n">
         <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0.0008168084075657662</v>

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -6420,6 +6420,151 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6453,7 +6598,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6681,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -6546,7 +6691,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -6598,7 +6743,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -5428,17 +5428,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -5472,56 +5472,138 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>147945</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CN_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SER_CN_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Source-reported aggregate; never derive it by summing subtype series.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN34" t="b">
+        <v>0</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -5531,22 +5613,22 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5690,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5753,7 +5835,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5762,13 +5844,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.004084042037828832</v>
+        <v>0</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -5898,7 +5980,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5907,13 +5989,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6043,7 +6125,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -6158,12 +6240,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6188,22 +6270,22 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6236,42 +6318,42 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6385,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6333,7 +6415,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6342,13 +6424,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6381,42 +6463,42 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6560,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6487,13 +6569,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6560,6 +6642,151 @@
         </is>
       </c>
       <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6691,7 +6918,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -6711,7 +6938,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6721,7 +6948,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -6792,6 +6792,151 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6825,7 +6970,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6908,7 +7053,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -6918,7 +7063,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -6970,7 +7115,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -5551,7 +5551,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -5551,7 +5551,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -5551,7 +5551,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -5551,7 +5551,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -4708,12 +4708,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4747,17 +4747,14 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.004900850445394598</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4786,42 +4783,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4850,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4883,7 +4880,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4892,17 +4889,14 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.004900850445394598</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4931,42 +4925,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4992,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5028,7 +5022,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -5037,17 +5031,14 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5076,42 +5067,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5134,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5173,7 +5164,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -5182,17 +5173,14 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.005717658852960364</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5221,42 +5209,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5276,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5318,12 +5306,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5332,12 +5320,9 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5371,12 +5356,12 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5391,12 +5376,12 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -5428,17 +5413,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5463,172 +5448,87 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>147945</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SER_CN_VIRAL_HEPATITIS</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>SER_CN_VIRAL_HEPATITIS</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>SRC_CN_CDC</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>病毒性肝炎</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>country:CN:national</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Source-reported aggregate; never derive it by summing subtype series.</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN34" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5660,12 +5560,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5690,12 +5590,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5704,12 +5604,9 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5738,42 +5635,42 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5702,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5835,12 +5732,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5849,12 +5746,9 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5883,42 +5777,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5980,22 +5874,22 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6125,22 +6019,22 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6270,22 +6164,22 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6385,12 +6279,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6415,22 +6309,22 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6463,42 +6357,42 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6530,12 +6424,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6560,22 +6454,22 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6608,42 +6502,42 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6675,12 +6569,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6705,26 +6599,23 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6753,42 +6644,42 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6820,12 +6711,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6850,26 +6741,23 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6898,42 +6786,3852 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>147945</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_CN_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_CN_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Source-reported aggregate; never derive it by summing subtype series.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW43" t="inlineStr">
+      <c r="AW51" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
+      <c r="AY51" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA43" t="inlineStr">
+      <c r="BA51" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB43" t="inlineStr">
+      <c r="BB51" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BC51" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>5</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>3</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6970,7 +10668,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -7053,7 +10751,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -7063,7 +10761,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -7115,7 +10813,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
